--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP-Adjusted.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP-Adjusted.xlsx
@@ -570,7 +570,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16.43</v>
+        <v>13.54</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -579,28 +579,28 @@
         <v>315</v>
       </c>
       <c r="E2">
-        <v>15.81</v>
+        <v>15.66</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>14284</v>
+        <v>17315</v>
       </c>
       <c r="J2">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="K2">
-        <v>16.17</v>
+        <v>13.31</v>
       </c>
       <c r="L2">
-        <v>16.69</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="3">
@@ -608,37 +608,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9.26</v>
+        <v>7.65</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>166</v>
+        <v>166.23</v>
       </c>
       <c r="E3">
-        <v>13.47</v>
+        <v>12.75</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>14</v>
+        <v>11.02</v>
       </c>
       <c r="I3">
-        <v>14284</v>
+        <v>17315</v>
       </c>
       <c r="J3">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K3">
-        <v>9.039999999999999</v>
+        <v>7.46</v>
       </c>
       <c r="L3">
-        <v>9.49</v>
+        <v>7.84</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP-Adjusted.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP-Adjusted.xlsx
@@ -422,7 +422,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16.92</v>
+        <v>18.71</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -431,28 +431,28 @@
         <v>315</v>
       </c>
       <c r="E2">
-        <v>15.79</v>
+        <v>16.21</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>14.77</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2">
-        <v>22.63</v>
+        <v>24.25</v>
       </c>
       <c r="I2">
-        <v>13863</v>
+        <v>17944</v>
       </c>
       <c r="J2">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="K2">
-        <v>16.65</v>
+        <v>18.47</v>
       </c>
       <c r="L2">
-        <v>17.18</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9.56</v>
+        <v>10.3</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -469,28 +469,28 @@
         <v>166.23</v>
       </c>
       <c r="E3">
-        <v>13.6</v>
+        <v>14.09</v>
       </c>
       <c r="F3">
-        <v>5.01</v>
+        <v>6.01</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>14.02</v>
+        <v>15.02</v>
       </c>
       <c r="I3">
-        <v>13863</v>
+        <v>17944</v>
       </c>
       <c r="J3">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="K3">
-        <v>9.33</v>
+        <v>10.09</v>
       </c>
       <c r="L3">
-        <v>9.779999999999999</v>
+        <v>10.51</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +570,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>13.54</v>
+        <v>14.9</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -579,28 +579,28 @@
         <v>315</v>
       </c>
       <c r="E2">
-        <v>15.66</v>
+        <v>16.31</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I2">
-        <v>17315</v>
+        <v>22538</v>
       </c>
       <c r="J2">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="K2">
-        <v>13.31</v>
+        <v>14.68</v>
       </c>
       <c r="L2">
-        <v>13.78</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="3">
@@ -608,7 +608,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -617,7 +617,7 @@
         <v>166.23</v>
       </c>
       <c r="E3">
-        <v>12.75</v>
+        <v>13.24</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -626,19 +626,19 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>11.02</v>
+        <v>12.02</v>
       </c>
       <c r="I3">
-        <v>17315</v>
+        <v>22538</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K3">
-        <v>7.46</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L3">
-        <v>7.84</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP-Adjusted.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP-Adjusted.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>18.71</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>315</v>
+        <v>1099</v>
       </c>
       <c r="E2">
-        <v>16.21</v>
+        <v>69.02</v>
       </c>
       <c r="F2">
-        <v>14.77</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H2">
-        <v>24.25</v>
+        <v>94</v>
       </c>
       <c r="I2">
-        <v>17944</v>
+        <v>17954</v>
       </c>
       <c r="J2">
-        <v>0.12</v>
+        <v>0.52</v>
       </c>
       <c r="K2">
-        <v>18.47</v>
+        <v>70.42</v>
       </c>
       <c r="L2">
-        <v>18.95</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="3">
@@ -460,37 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>10.3</v>
+        <v>41.19</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>166.23</v>
+        <v>1073.99</v>
       </c>
       <c r="E3">
-        <v>14.09</v>
+        <v>60.36</v>
       </c>
       <c r="F3">
-        <v>6.01</v>
+        <v>20.03</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>15.02</v>
+        <v>60.08</v>
       </c>
       <c r="I3">
-        <v>17944</v>
+        <v>17954</v>
       </c>
       <c r="J3">
-        <v>0.11</v>
+        <v>0.45</v>
       </c>
       <c r="K3">
-        <v>10.09</v>
+        <v>40.31</v>
       </c>
       <c r="L3">
-        <v>10.51</v>
+        <v>42.07</v>
       </c>
     </row>
   </sheetData>
@@ -570,37 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>14.9</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>315</v>
+        <v>1099</v>
       </c>
       <c r="E2">
-        <v>16.31</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I2">
-        <v>22538</v>
+        <v>18143</v>
       </c>
       <c r="J2">
-        <v>0.11</v>
+        <v>0.51</v>
       </c>
       <c r="K2">
-        <v>14.68</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="L2">
-        <v>15.11</v>
+        <v>71.69</v>
       </c>
     </row>
     <row r="3">
@@ -608,37 +608,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.199999999999999</v>
+        <v>40.76</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>166.23</v>
+        <v>1073.99</v>
       </c>
       <c r="E3">
-        <v>13.24</v>
+        <v>60.19</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>19.03</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>12.02</v>
+        <v>59.37</v>
       </c>
       <c r="I3">
-        <v>22538</v>
+        <v>18143</v>
       </c>
       <c r="J3">
-        <v>0.09</v>
+        <v>0.45</v>
       </c>
       <c r="K3">
-        <v>8.029999999999999</v>
+        <v>39.88</v>
       </c>
       <c r="L3">
-        <v>8.369999999999999</v>
+        <v>41.64</v>
       </c>
     </row>
   </sheetData>
